--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486319_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486319_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.52</v>
+        <v>1.0523</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1363</v>
+        <v>2.7178</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6163</v>
+        <v>-1.6655</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3057</v>
+        <v>3.0986</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0762</v>
+        <v>0.9487</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2295</v>
+        <v>2.1499</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1941</v>
+        <v>4.6033</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6387</v>
+        <v>1.3504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5554</v>
+        <v>3.2528</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4998</v>
+        <v>-1.5047</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7149</v>
+        <v>-0.4018</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7849</v>
+        <v>-1.1029</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3683</v>
+        <v>-0.4813</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9421</v>
+        <v>-0.5804</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5738</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9176</v>
+        <v>1.0035</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1221</v>
+        <v>1.4657</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7955</v>
+        <v>-0.4622</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8276</v>
+        <v>-0.3057</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6506</v>
+        <v>-0.0762</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1769</v>
+        <v>-0.2295</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1408</v>
+        <v>1.1941</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0643</v>
+        <v>0.6387</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0765</v>
+        <v>0.5554</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9683</v>
+        <v>-1.4998</v>
       </c>
       <c r="N3" t="n">
         <v>-0.7149</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2534</v>
+        <v>-0.7849</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7675</v>
+        <v>-0.1481</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8736</v>
+        <v>0.2716</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8938</v>
+        <v>-0.4197</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1952</v>
+        <v>0.3698</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4204</v>
+        <v>-0.1729</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2708</v>
+        <v>-0.2433</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8504</v>
+        <v>0.0704</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0986</v>
+        <v>-0.6653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9487</v>
+        <v>0.3133</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1499</v>
+        <v>-0.9785</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6033</v>
+        <v>-0.3983</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3504</v>
+        <v>0.3467</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2528</v>
+        <v>-0.7451</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5047</v>
+        <v>-0.267</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4018</v>
+        <v>-0.0335</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1029</v>
+        <v>-0.2335</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1133</v>
+        <v>0.0574</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0274</v>
+        <v>0.155</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0858</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4272</v>
+        <v>-0.2179</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4668</v>
+        <v>1.2919</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0396</v>
+        <v>-1.5098</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6653</v>
+        <v>-2.2128</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3133</v>
+        <v>1.5906</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9785</v>
+        <v>-3.8034</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3983</v>
+        <v>0.1189</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3467</v>
+        <v>2.3724</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7451</v>
+        <v>-2.2535</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.267</v>
+        <v>-2.3318</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0335</v>
+        <v>-0.7819</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2335</v>
+        <v>-1.5499</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.197</v>
+        <v>-0.4602</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1285</v>
+        <v>-0.2656</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. PENO</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8824</v>
+        <v>-0.3463</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3164</v>
+        <v>-0.772</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1989</v>
+        <v>0.4257</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1494</v>
+        <v>-0.8276</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0609</v>
+        <v>-0.6506</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0885</v>
+        <v>-0.1769</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.1408</v>
       </c>
       <c r="K6" t="n">
-        <v>0.073</v>
+        <v>0.0643</v>
       </c>
       <c r="L6" t="n">
-        <v>0.612</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8344</v>
+        <v>-0.9683</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1339</v>
+        <v>-0.7149</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7004</v>
+        <v>-0.2534</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.298</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>-0.0204</v>
       </c>
       <c r="U6" t="n">
-        <v>0.113</v>
+        <v>0.5239</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>S. PENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0918</v>
+        <v>-0.6589</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6646</v>
+        <v>0.54</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7564</v>
+        <v>-1.1989</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2128</v>
+        <v>-0.1494</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5906</v>
+        <v>-0.0609</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.8034</v>
+        <v>-0.0885</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1189</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3724</v>
+        <v>0.073</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.2535</v>
+        <v>0.612</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3318</v>
+        <v>-0.8344</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7819</v>
+        <v>-0.1339</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5499</v>
+        <v>-0.7004</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3341</v>
+        <v>-0.0745</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.1875</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5122</v>
+        <v>0.113</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4552</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4541</v>
+        <v>-1.258</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4546</v>
+        <v>-0.0454</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-1.2126</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.541</v>
+        <v>-0.4988</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2105</v>
+        <v>0.4773</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7515</v>
+        <v>-0.9762</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5286</v>
+        <v>2.0203</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7948</v>
+        <v>1.4266</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2661</v>
+        <v>0.5937</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0696</v>
+        <v>-2.5191</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5843</v>
+        <v>-0.9493</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4854</v>
+        <v>-1.5698</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7401</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.262</v>
+        <v>-0.1067</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3509</v>
+        <v>-0.7607</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6128</v>
+        <v>0.654</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4583</v>
+        <v>-1.6938</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0035</v>
+        <v>-0.3861</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4617</v>
+        <v>-1.3077</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5505</v>
+        <v>-0.541</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4258</v>
+        <v>1.2105</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.9763</v>
+        <v>-1.7515</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6538</v>
+        <v>1.5286</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3901</v>
+        <v>1.7948</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0439</v>
+        <v>-0.2661</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8967</v>
+        <v>-2.0696</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9643</v>
+        <v>-0.5843</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9324</v>
+        <v>-1.4854</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5926</v>
+        <v>0.0222</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1454</v>
+        <v>-0.2824</v>
       </c>
       <c r="U9" t="n">
-        <v>0.738</v>
+        <v>0.3046</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4997</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8902</v>
+        <v>0.7602</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3904</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6857</v>
+        <v>-1.7789</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3807</v>
+        <v>-0.0398</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.305</v>
+        <v>-1.7391</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4988</v>
+        <v>-3.5505</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4773</v>
+        <v>0.4258</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9762</v>
+        <v>-3.9763</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0203</v>
+        <v>-0.6538</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4266</v>
+        <v>1.3901</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5937</v>
+        <v>-2.0439</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5191</v>
+        <v>-2.8967</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9493</v>
+        <v>-0.9643</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5698</v>
+        <v>-1.9324</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5344</v>
+        <v>0.2719</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0959</v>
+        <v>-0.1887</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5615</v>
+        <v>0.4605</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4997</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5976</v>
+        <v>-4.1495</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0908</v>
+        <v>-2.5811</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5067</v>
+        <v>-1.5684</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4266</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>1.002</v>
+        <v>0.45</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1202</v>
+        <v>-0.3701</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8818</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5204</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2836</v>
+        <v>-4.4599</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6095</v>
+        <v>-4.0939</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6742</v>
+        <v>-0.3659</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2283</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.858</v>
+        <v>-0.0342</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3014</v>
+        <v>-0.7859</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4434</v>
+        <v>0.7516</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3698</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.0227</v>
+        <v>-12.6803</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4887</v>
+        <v>-2.146199999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-10.534</v>
@@ -1435,7 +1435,7 @@
         <v>-9.307400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.558</v>
+        <v>3.558000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-12.8653</v>
@@ -1453,7 +1453,7 @@
         <v>-18.1821</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.575799999999999</v>
+        <v>-7.5758</v>
       </c>
       <c r="O13" t="n">
         <v>-10.6063</v>
@@ -1468,13 +1468,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3423999999999999</v>
+        <v>-1.040834085586084e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.2866</v>
+        <v>-2.9442</v>
       </c>
       <c r="U13" t="n">
-        <v>2.944</v>
+        <v>2.9439</v>
       </c>
       <c r="V13" t="n">
         <v>2.0647</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4715</v>
+        <v>5.8473</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3639</v>
+        <v>4.1404</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1076</v>
+        <v>1.7069</v>
       </c>
       <c r="G14" t="n">
         <v>4.1337</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9898</v>
+        <v>0.3656</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2704</v>
+        <v>-0.4939</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2602</v>
+        <v>0.8595</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1745</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8947</v>
+        <v>4.9794</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9253</v>
+        <v>4.7017</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0306</v>
+        <v>0.2776</v>
       </c>
       <c r="G15" t="n">
         <v>1.4611</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.262</v>
+        <v>-0.1772</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3268</v>
+        <v>-0.5504</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0649</v>
+        <v>0.3731</v>
       </c>
       <c r="V15" t="n">
         <v>1.5204</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9087</v>
+        <v>3.7256</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3179</v>
+        <v>0.765</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5908</v>
+        <v>2.9606</v>
       </c>
       <c r="G16" t="n">
         <v>1.0197</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8734</v>
+        <v>-0.0565</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2774</v>
+        <v>-0.8304</v>
       </c>
       <c r="U16" t="n">
-        <v>0.404</v>
+        <v>0.7739</v>
       </c>
       <c r="V16" t="n">
         <v>0.3698</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6589</v>
+        <v>3.1675</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3584</v>
+        <v>2.8054</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3005</v>
+        <v>0.3621</v>
       </c>
       <c r="G17" t="n">
         <v>3.7256</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7845</v>
+        <v>-0.2758</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1524</v>
+        <v>-0.7054</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3679</v>
+        <v>0.4296</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9347</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.68</v>
+        <v>0.2522</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7451</v>
+        <v>0.4098</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.1576</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5755</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8204</v>
+        <v>0.3927</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6886</v>
+        <v>0.3533</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1318</v>
+        <v>0.0394</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2001</v>
+        <v>-0.0108</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.8168</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3719</v>
+        <v>-0.8276</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5469000000000001</v>
+        <v>1.552</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1947</v>
+        <v>0.5535</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3522</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1695</v>
+        <v>3.2478</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0547</v>
+        <v>2.0804</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>1.1674</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7164</v>
+        <v>-1.6959</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2495</v>
+        <v>-1.5269</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.467</v>
+        <v>-0.1689</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2245</v>
+        <v>-0.4975</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4026</v>
+        <v>-0.256</v>
       </c>
       <c r="U19" t="n">
-        <v>0.822</v>
+        <v>-0.2415</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0242</v>
+        <v>-0.0357</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0443</v>
+        <v>-0.079</v>
       </c>
       <c r="G20" t="n">
         <v>0.082</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1062</v>
+        <v>-0.1178</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0377</v>
+        <v>-0.161</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2024</v>
+        <v>-0.4434</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3822</v>
+        <v>0.2368</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1798</v>
+        <v>-0.6802</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6909</v>
+        <v>-0.1947</v>
       </c>
       <c r="I21" t="n">
-        <v>0.761</v>
+        <v>-0.3522</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0667</v>
+        <v>0.1695</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.356</v>
+        <v>0.0547</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2893</v>
+        <v>0.1147</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1369</v>
+        <v>-0.7164</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3348</v>
+        <v>-0.2495</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4717</v>
+        <v>-0.467</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6627</v>
+        <v>0.581</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2704</v>
+        <v>0.0673</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9331</v>
+        <v>0.5137</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3576</v>
+        <v>-0.58</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5933</v>
+        <v>-2.6057</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9509</v>
+        <v>2.0257</v>
       </c>
       <c r="G22" t="n">
-        <v>1.552</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5535</v>
+        <v>-1.6909</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2478</v>
+        <v>-1.0667</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0804</v>
+        <v>-1.356</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1674</v>
+        <v>0.2893</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6959</v>
+        <v>0.1369</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5269</v>
+        <v>-0.3348</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1689</v>
+        <v>0.4717</v>
       </c>
       <c r="P22" t="n">
         <v>-0.87</v>
@@ -2170,19 +2170,19 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8443000000000001</v>
+        <v>0.2851</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4795</v>
+        <v>-0.4939</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3648</v>
+        <v>0.779</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1952</v>
+        <v>0.9347</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1689</v>
+        <v>-1.2383</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6646</v>
+        <v>-0.8881</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5043</v>
+        <v>-0.3502</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5132</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1268</v>
+        <v>0.0574</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2091</v>
+        <v>-0.0144</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0823</v>
+        <v>0.0718</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.038</v>
+        <v>-2.641</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2265</v>
+        <v>0.1087</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8114</v>
+        <v>-2.7498</v>
       </c>
       <c r="G24" t="n">
         <v>0.8987000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.2145</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.399</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2125</v>
+        <v>-0.1508</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4552</v>
@@ -2362,10 +2362,10 @@
         <v>13.0228</v>
       </c>
       <c r="E25" t="n">
-        <v>10.5342</v>
+        <v>10.5341</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4888</v>
+        <v>2.4885</v>
       </c>
       <c r="G25" t="n">
         <v>9.3073</v>
@@ -2380,7 +2380,7 @@
         <v>18.1821</v>
       </c>
       <c r="K25" t="n">
-        <v>7.5756</v>
+        <v>7.575600000000001</v>
       </c>
       <c r="L25" t="n">
         <v>10.6063</v>
@@ -2392,7 +2392,7 @@
         <v>-11.1337</v>
       </c>
       <c r="O25" t="n">
-        <v>2.2588</v>
+        <v>2.258799999999999</v>
       </c>
       <c r="P25" t="n">
         <v>5.4377</v>
@@ -2404,13 +2404,13 @@
         <v>14.1378</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3423999999999999</v>
+        <v>0.3424999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.9441</v>
+        <v>-2.9442</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2866</v>
+        <v>3.2867</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0647</v>
